--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -670,7 +670,7 @@
         <v>152</v>
       </c>
       <c r="K4" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L4" t="n">
         <v>83</v>
@@ -691,7 +691,7 @@
         <v>40</v>
       </c>
       <c r="R4" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9">
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">

--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -2031,7 +2031,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Wizz Air</t>
+          <t>Qatar Cargo</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Qatar Cargo</t>
+          <t>Wizz Air</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2120,10 +2120,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>

--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -670,7 +670,7 @@
         <v>152</v>
       </c>
       <c r="K4" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L4" t="n">
         <v>83</v>
@@ -691,7 +691,7 @@
         <v>40</v>
       </c>
       <c r="R4" t="n">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="9">
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
@@ -2031,7 +2031,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Qatar Cargo</t>
+          <t>Wizz Air</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Wizz Air</t>
+          <t>Qatar Cargo</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2120,10 +2120,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>

--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -670,7 +670,7 @@
         <v>152</v>
       </c>
       <c r="K4" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L4" t="n">
         <v>83</v>
@@ -691,7 +691,7 @@
         <v>40</v>
       </c>
       <c r="R4" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9">
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -2031,7 +2031,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Wizz Air</t>
+          <t>Qatar Cargo</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Qatar Cargo</t>
+          <t>Wizz Air</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2120,10 +2120,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">

--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -530,10 +530,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="D2" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1961</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="3">
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K3" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="L3" t="n">
         <v>56</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="4">
@@ -716,10 +716,10 @@
         <v>149</v>
       </c>
       <c r="G5" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H5" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="6">
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         <v>126</v>
       </c>
       <c r="R7" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8">
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G10" t="n">
         <v>24</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>68</v>
       </c>
       <c r="R12" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13">
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M13" t="n">
         <v>6</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14">
@@ -2031,7 +2031,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Qatar Cargo</t>
+          <t>Wizz Air</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Wizz Air</t>
+          <t>Qatar Cargo</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2120,10 +2120,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Brussels Airlines</t>
+          <t>Vueling</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2175,16 +2175,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M30" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Vueling</t>
+          <t>Brussels Airlines</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2233,16 +2233,16 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">

--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -530,10 +530,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="D2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1965</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="3">
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K3" t="n">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="L3" t="n">
         <v>56</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1315</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="4">
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R7" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -1155,7 +1155,7 @@
         <v>68</v>
       </c>
       <c r="R12" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13">
@@ -1299,7 +1299,7 @@
         <v>85</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16">

--- a/aircraft/reports/airline-aircraft-type-heatmap.xlsx
+++ b/aircraft/reports/airline-aircraft-type-heatmap.xlsx
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="D2" t="n">
         <v>297</v>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="3">
@@ -719,7 +719,7 @@
         <v>276</v>
       </c>
       <c r="H5" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="6">
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -795,10 +795,10 @@
         <v>114</v>
       </c>
       <c r="N6" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O6" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P6" t="n">
         <v>37</v>
@@ -807,7 +807,7 @@
         <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -1155,7 +1155,7 @@
         <v>68</v>
       </c>
       <c r="R12" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13">
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L13" t="n">
         <v>29</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M15" t="n">
         <v>51</v>
@@ -1329,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16">
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16" t="n">
         <v>25</v>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>Cargolux</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1433,25 +1433,25 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Cargolux</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1464,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1491,19 +1491,19 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19">
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
@@ -2495,7 +2495,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Icelandair</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2511,13 +2511,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>8</v>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2538,13 +2538,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>69</v>
@@ -2553,7 +2553,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Icelandair</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2569,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2596,16 +2596,16 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R37" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
